--- a/Excel-files/purchase_Reactivate.xlsx
+++ b/Excel-files/purchase_Reactivate.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS01503\Documents\load testing Script-BSS\Excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D27177-BCF7-4154-9DF3-6900871766D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13410707-7CAF-4511-AE76-9EF353CADBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="-13365" windowWidth="19185" windowHeight="10065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase (Reactive)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="204">
   <si>
     <r>
       <rPr>
@@ -88,35 +88,614 @@
     </r>
   </si>
   <si>
-    <t>SID2609000947</t>
-  </si>
-  <si>
-    <t>OID1686</t>
-  </si>
-  <si>
-    <t>SID2609000948</t>
-  </si>
-  <si>
-    <t>OID1688</t>
-  </si>
-  <si>
-    <t>SID2609000949</t>
-  </si>
-  <si>
-    <t>OID1685</t>
-  </si>
-  <si>
-    <t>SID2609000950</t>
-  </si>
-  <si>
-    <t>OID1684</t>
+    <t>SID2609017233</t>
+  </si>
+  <si>
+    <t>OID386</t>
+  </si>
+  <si>
+    <t>SID2609017211</t>
+  </si>
+  <si>
+    <t>OID385</t>
+  </si>
+  <si>
+    <t>SID2609017230</t>
+  </si>
+  <si>
+    <t>OID384</t>
+  </si>
+  <si>
+    <t>SID2609017237</t>
+  </si>
+  <si>
+    <t>OID383</t>
+  </si>
+  <si>
+    <t>SID2609017198</t>
+  </si>
+  <si>
+    <t>OID382</t>
+  </si>
+  <si>
+    <t>SID2609017195</t>
+  </si>
+  <si>
+    <t>OID381</t>
+  </si>
+  <si>
+    <t>SID2609017232</t>
+  </si>
+  <si>
+    <t>OID380</t>
+  </si>
+  <si>
+    <t>SID2609017221</t>
+  </si>
+  <si>
+    <t>OID379</t>
+  </si>
+  <si>
+    <t>SID2609017219</t>
+  </si>
+  <si>
+    <t>OID378</t>
+  </si>
+  <si>
+    <t>SID2609017216</t>
+  </si>
+  <si>
+    <t>OID377</t>
+  </si>
+  <si>
+    <t>SID2609017191</t>
+  </si>
+  <si>
+    <t>OID376</t>
+  </si>
+  <si>
+    <t>SID2609017188</t>
+  </si>
+  <si>
+    <t>OID375</t>
+  </si>
+  <si>
+    <t>SID2609017236</t>
+  </si>
+  <si>
+    <t>OID374</t>
+  </si>
+  <si>
+    <t>SID2609017210</t>
+  </si>
+  <si>
+    <t>OID373</t>
+  </si>
+  <si>
+    <t>SID2609017207</t>
+  </si>
+  <si>
+    <t>OID372</t>
+  </si>
+  <si>
+    <t>SID2609017200</t>
+  </si>
+  <si>
+    <t>OID371</t>
+  </si>
+  <si>
+    <t>SID2609017243</t>
+  </si>
+  <si>
+    <t>OID370</t>
+  </si>
+  <si>
+    <t>SID2609017228</t>
+  </si>
+  <si>
+    <t>OID369</t>
+  </si>
+  <si>
+    <t>SID2609017176</t>
+  </si>
+  <si>
+    <t>OID368</t>
+  </si>
+  <si>
+    <t>SID2609017234</t>
+  </si>
+  <si>
+    <t>OID367</t>
+  </si>
+  <si>
+    <t>SID2609017209</t>
+  </si>
+  <si>
+    <t>OID366</t>
+  </si>
+  <si>
+    <t>SID2609017189</t>
+  </si>
+  <si>
+    <t>OID365</t>
+  </si>
+  <si>
+    <t>SID2609017173</t>
+  </si>
+  <si>
+    <t>OID364</t>
+  </si>
+  <si>
+    <t>SID2609017227</t>
+  </si>
+  <si>
+    <t>OID363</t>
+  </si>
+  <si>
+    <t>SID2609017206</t>
+  </si>
+  <si>
+    <t>OID362</t>
+  </si>
+  <si>
+    <t>SID2609017182</t>
+  </si>
+  <si>
+    <t>OID361</t>
+  </si>
+  <si>
+    <t>SID2609017163</t>
+  </si>
+  <si>
+    <t>OID360</t>
+  </si>
+  <si>
+    <t>SID2609017212</t>
+  </si>
+  <si>
+    <t>OID359</t>
+  </si>
+  <si>
+    <t>SID2609017203</t>
+  </si>
+  <si>
+    <t>OID358</t>
+  </si>
+  <si>
+    <t>SID2609017225</t>
+  </si>
+  <si>
+    <t>OID357</t>
+  </si>
+  <si>
+    <t>SID2609017186</t>
+  </si>
+  <si>
+    <t>OID356</t>
+  </si>
+  <si>
+    <t>SID2609017208</t>
+  </si>
+  <si>
+    <t>OID355</t>
+  </si>
+  <si>
+    <t>SID2609017240</t>
+  </si>
+  <si>
+    <t>OID354</t>
+  </si>
+  <si>
+    <t>SID2609017222</t>
+  </si>
+  <si>
+    <t>OID353</t>
+  </si>
+  <si>
+    <t>SID2609017184</t>
+  </si>
+  <si>
+    <t>OID352</t>
+  </si>
+  <si>
+    <t>SID2609017202</t>
+  </si>
+  <si>
+    <t>OID351</t>
+  </si>
+  <si>
+    <t>SID2609017224</t>
+  </si>
+  <si>
+    <t>OID350</t>
+  </si>
+  <si>
+    <t>SID2609017177</t>
+  </si>
+  <si>
+    <t>OID349</t>
+  </si>
+  <si>
+    <t>SID2609017192</t>
+  </si>
+  <si>
+    <t>OID348</t>
+  </si>
+  <si>
+    <t>SID2609017178</t>
+  </si>
+  <si>
+    <t>OID347</t>
+  </si>
+  <si>
+    <t>SID2609017187</t>
+  </si>
+  <si>
+    <t>OID346</t>
+  </si>
+  <si>
+    <t>SID2609017157</t>
+  </si>
+  <si>
+    <t>OID345</t>
+  </si>
+  <si>
+    <t>SID2609017197</t>
+  </si>
+  <si>
+    <t>OID344</t>
+  </si>
+  <si>
+    <t>SID2609017185</t>
+  </si>
+  <si>
+    <t>OID343</t>
+  </si>
+  <si>
+    <t>SID2609017154</t>
+  </si>
+  <si>
+    <t>OID342</t>
+  </si>
+  <si>
+    <t>SID2609017193</t>
+  </si>
+  <si>
+    <t>OID341</t>
+  </si>
+  <si>
+    <t>SID2609017218</t>
+  </si>
+  <si>
+    <t>OID340</t>
+  </si>
+  <si>
+    <t>SID2609017151</t>
+  </si>
+  <si>
+    <t>OID339</t>
+  </si>
+  <si>
+    <t>SID2609017172</t>
+  </si>
+  <si>
+    <t>OID338</t>
+  </si>
+  <si>
+    <t>SID2609017215</t>
+  </si>
+  <si>
+    <t>OID337</t>
+  </si>
+  <si>
+    <t>SID2609017148</t>
+  </si>
+  <si>
+    <t>OID336</t>
+  </si>
+  <si>
+    <t>SID2609017183</t>
+  </si>
+  <si>
+    <t>OID335</t>
+  </si>
+  <si>
+    <t>SID2609017161</t>
+  </si>
+  <si>
+    <t>OID334</t>
+  </si>
+  <si>
+    <t>SID2609017205</t>
+  </si>
+  <si>
+    <t>OID333</t>
+  </si>
+  <si>
+    <t>SID2609017179</t>
+  </si>
+  <si>
+    <t>OID332</t>
+  </si>
+  <si>
+    <t>SID2609017155</t>
+  </si>
+  <si>
+    <t>OID331</t>
+  </si>
+  <si>
+    <t>SID2609017199</t>
+  </si>
+  <si>
+    <t>OID330</t>
+  </si>
+  <si>
+    <t>SID2609017201</t>
+  </si>
+  <si>
+    <t>OID329</t>
+  </si>
+  <si>
+    <t>SID2609017153</t>
+  </si>
+  <si>
+    <t>OID328</t>
+  </si>
+  <si>
+    <t>SID2609017181</t>
+  </si>
+  <si>
+    <t>OID327</t>
+  </si>
+  <si>
+    <t>SID2609017169</t>
+  </si>
+  <si>
+    <t>OID326</t>
+  </si>
+  <si>
+    <t>SID2609017167</t>
+  </si>
+  <si>
+    <t>OID325</t>
+  </si>
+  <si>
+    <t>SID2609017213</t>
+  </si>
+  <si>
+    <t>OID324</t>
+  </si>
+  <si>
+    <t>SID2609017168</t>
+  </si>
+  <si>
+    <t>OID323</t>
+  </si>
+  <si>
+    <t>SID2609017150</t>
+  </si>
+  <si>
+    <t>OID322</t>
+  </si>
+  <si>
+    <t>SID2609017175</t>
+  </si>
+  <si>
+    <t>OID321</t>
+  </si>
+  <si>
+    <t>SID2609017194</t>
+  </si>
+  <si>
+    <t>OID320</t>
+  </si>
+  <si>
+    <t>SID2609017138</t>
+  </si>
+  <si>
+    <t>OID319</t>
+  </si>
+  <si>
+    <t>SID2609017204</t>
+  </si>
+  <si>
+    <t>OID318</t>
+  </si>
+  <si>
+    <t>SID2609017190</t>
+  </si>
+  <si>
+    <t>OID317</t>
+  </si>
+  <si>
+    <t>SID2609017162</t>
+  </si>
+  <si>
+    <t>OID316</t>
+  </si>
+  <si>
+    <t>SID2609017170</t>
+  </si>
+  <si>
+    <t>OID315</t>
+  </si>
+  <si>
+    <t>SID2609017164</t>
+  </si>
+  <si>
+    <t>OID314</t>
+  </si>
+  <si>
+    <t>SID2609017159</t>
+  </si>
+  <si>
+    <t>OID313</t>
+  </si>
+  <si>
+    <t>SID2609017196</t>
+  </si>
+  <si>
+    <t>OID312</t>
+  </si>
+  <si>
+    <t>SID2609017180</t>
+  </si>
+  <si>
+    <t>OID311</t>
+  </si>
+  <si>
+    <t>SID2609017156</t>
+  </si>
+  <si>
+    <t>OID310</t>
+  </si>
+  <si>
+    <t>SID2609017166</t>
+  </si>
+  <si>
+    <t>OID309</t>
+  </si>
+  <si>
+    <t>SID2609017171</t>
+  </si>
+  <si>
+    <t>OID308</t>
+  </si>
+  <si>
+    <t>SID2609017145</t>
+  </si>
+  <si>
+    <t>OID307</t>
+  </si>
+  <si>
+    <t>SID2609017160</t>
+  </si>
+  <si>
+    <t>OID306</t>
+  </si>
+  <si>
+    <t>SID2609017147</t>
+  </si>
+  <si>
+    <t>OID305</t>
+  </si>
+  <si>
+    <t>SID2609017142</t>
+  </si>
+  <si>
+    <t>OID304</t>
+  </si>
+  <si>
+    <t>SID2609017144</t>
+  </si>
+  <si>
+    <t>OID303</t>
+  </si>
+  <si>
+    <t>SID2609017152</t>
+  </si>
+  <si>
+    <t>OID302</t>
+  </si>
+  <si>
+    <t>SID2609017158</t>
+  </si>
+  <si>
+    <t>OID301</t>
+  </si>
+  <si>
+    <t>SID2609017149</t>
+  </si>
+  <si>
+    <t>OID300</t>
+  </si>
+  <si>
+    <t>SID2609017140</t>
+  </si>
+  <si>
+    <t>OID299</t>
+  </si>
+  <si>
+    <t>SID2609017146</t>
+  </si>
+  <si>
+    <t>OID298</t>
+  </si>
+  <si>
+    <t>SID2609017174</t>
+  </si>
+  <si>
+    <t>OID297</t>
+  </si>
+  <si>
+    <t>SID2609017141</t>
+  </si>
+  <si>
+    <t>OID296</t>
+  </si>
+  <si>
+    <t>SID2609017165</t>
+  </si>
+  <si>
+    <t>OID295</t>
+  </si>
+  <si>
+    <t>SID2609017143</t>
+  </si>
+  <si>
+    <t>OID294</t>
+  </si>
+  <si>
+    <t>SID2609017139</t>
+  </si>
+  <si>
+    <t>OID293</t>
+  </si>
+  <si>
+    <t>SID2609017137</t>
+  </si>
+  <si>
+    <t>OID292</t>
+  </si>
+  <si>
+    <t>SID2609017135</t>
+  </si>
+  <si>
+    <t>OID291</t>
+  </si>
+  <si>
+    <t>SID2609017133</t>
+  </si>
+  <si>
+    <t>OID290</t>
+  </si>
+  <si>
+    <t>SID2609017136</t>
+  </si>
+  <si>
+    <t>OID289</t>
+  </si>
+  <si>
+    <t>SID2609017132</t>
+  </si>
+  <si>
+    <t>OID288</t>
+  </si>
+  <si>
+    <t>SID2609017134</t>
+  </si>
+  <si>
+    <t>OID287</t>
+  </si>
+  <si>
+    <t>Reactivated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -138,8 +717,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,8 +738,14 @@
         <fgColor rgb="FF467D45"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -175,14 +768,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -518,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
@@ -538,35 +1167,1103 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="C2" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="C3" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="C4" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C56" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C62" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C65" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C77" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C78" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C79" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C80" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C81" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C82" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C83" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C86" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C87" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C88" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C89" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C90" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C91" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C92" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C93" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C94" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C96" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C97" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C98" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C99" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C100" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C101" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
